--- a/data/keuangan.xlsx
+++ b/data/keuangan.xlsx
@@ -17,8 +17,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -49,8 +49,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -453,7 +454,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>46187.74002378473</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -481,7 +482,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>46187.74002378473</v>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,7 +510,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>46187.74002378473</v>
       </c>
       <c r="B4" t="inlineStr">
@@ -537,7 +538,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>46187.74002378473</v>
       </c>
       <c r="B5" t="inlineStr">
@@ -565,7 +566,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>46188.74002378473</v>
       </c>
       <c r="B6" t="inlineStr">

--- a/data/keuangan.xlsx
+++ b/data/keuangan.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
